--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2023_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2023_magallanes_y_la_antartica_chilena.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Total_Regional" sheetId="1" r:id="rId1"/>
     <sheet name="Por_Sexo" sheetId="2" r:id="rId2"/>
-    <sheet name="Por_Edad" sheetId="3" r:id="rId3"/>
+    <sheet name="Por_Prov" sheetId="3" r:id="rId3"/>
+    <sheet name="Por_Edad" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -353,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -364,19 +365,44 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Residentes</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Proyectada</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Cobertura</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria_lbl</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Total
-Regional</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B2">
+        <v>184445</v>
+      </c>
+      <c r="C2">
+        <v>182217</v>
+      </c>
+      <c r="D2">
         <v>101.2227179681369</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -424,17 +450,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="C2">
-        <v>93326</v>
+        <v>91119</v>
       </c>
       <c r="D2">
-        <v>92686</v>
+        <v>89531</v>
       </c>
       <c r="E2">
-        <v>100.69050342015</v>
+        <v>101.773687326178</v>
       </c>
     </row>
     <row r="3">
@@ -445,17 +471,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="C3">
-        <v>91119</v>
+        <v>93326</v>
       </c>
       <c r="D3">
-        <v>89531</v>
+        <v>92686</v>
       </c>
       <c r="E3">
-        <v>101.773687326178</v>
+        <v>100.69050342015</v>
       </c>
     </row>
   </sheetData>
@@ -465,7 +491,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -476,7 +502,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tramo_Edad</t>
+          <t>Provincia</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -503,17 +529,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0-14</t>
+          <t>Antártica Chilena</t>
         </is>
       </c>
       <c r="C2">
-        <v>29310</v>
+        <v>1996</v>
       </c>
       <c r="D2">
-        <v>31501</v>
+        <v>1973</v>
       </c>
       <c r="E2">
-        <v>93.04466524872225</v>
+        <v>101.1657374556513</v>
       </c>
     </row>
     <row r="3">
@@ -524,17 +550,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15-29</t>
+          <t>Tierra del Fuego</t>
         </is>
       </c>
       <c r="C3">
-        <v>36558</v>
+        <v>8210</v>
       </c>
       <c r="D3">
-        <v>37107</v>
+        <v>8527</v>
       </c>
       <c r="E3">
-        <v>98.52049478535048</v>
+        <v>96.28239709159142</v>
       </c>
     </row>
     <row r="4">
@@ -545,17 +571,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30-44</t>
+          <t>Última Esperanza</t>
         </is>
       </c>
       <c r="C4">
-        <v>45465</v>
+        <v>29456</v>
       </c>
       <c r="D4">
-        <v>44117</v>
+        <v>25516</v>
       </c>
       <c r="E4">
-        <v>103.0555114808351</v>
+        <v>115.441291738517</v>
       </c>
     </row>
     <row r="5">
@@ -566,17 +592,138 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45-64</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="C5">
-        <v>45985</v>
+        <v>144761</v>
       </c>
       <c r="D5">
-        <v>44374</v>
+        <v>146053</v>
       </c>
       <c r="E5">
-        <v>103.6305043493938</v>
+        <v>99.115389618837</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Desagregación 1</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Tramo_Edad</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Residentes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Proyectada</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>7653</v>
+      </c>
+      <c r="D2">
+        <v>9751</v>
+      </c>
+      <c r="E2">
+        <v>78.48425802481796</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5-9</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>10188</v>
+      </c>
+      <c r="D3">
+        <v>10447</v>
+      </c>
+      <c r="E3">
+        <v>97.52081937398296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10-14</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>11469</v>
+      </c>
+      <c r="D4">
+        <v>11303</v>
+      </c>
+      <c r="E4">
+        <v>101.4686366451385</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15-19</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>11331</v>
+      </c>
+      <c r="D5">
+        <v>11174</v>
+      </c>
+      <c r="E5">
+        <v>101.4050474315375</v>
       </c>
     </row>
     <row r="6">
@@ -587,17 +734,269 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>20-24</t>
         </is>
       </c>
       <c r="C6">
-        <v>27127</v>
+        <v>11268</v>
       </c>
       <c r="D6">
-        <v>25118</v>
+        <v>11593</v>
       </c>
       <c r="E6">
-        <v>107.9982482681742</v>
+        <v>97.1965841456051</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>25-29</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>13959</v>
+      </c>
+      <c r="D7">
+        <v>14340</v>
+      </c>
+      <c r="E7">
+        <v>97.34309623430963</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30-34</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>16101</v>
+      </c>
+      <c r="D8">
+        <v>15976</v>
+      </c>
+      <c r="E8">
+        <v>100.7824236354532</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>35-39</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>15616</v>
+      </c>
+      <c r="D9">
+        <v>14530</v>
+      </c>
+      <c r="E9">
+        <v>107.4741913282863</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>40-44</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>13748</v>
+      </c>
+      <c r="D10">
+        <v>13611</v>
+      </c>
+      <c r="E10">
+        <v>101.0065388288884</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>45-49</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>12591</v>
+      </c>
+      <c r="D11">
+        <v>12303</v>
+      </c>
+      <c r="E11">
+        <v>102.3408924652524</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>50-54</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>11136</v>
+      </c>
+      <c r="D12">
+        <v>10679</v>
+      </c>
+      <c r="E12">
+        <v>104.2794269126323</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>55-59</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>11242</v>
+      </c>
+      <c r="D13">
+        <v>10832</v>
+      </c>
+      <c r="E13">
+        <v>103.7850812407681</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>60-64</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>11016</v>
+      </c>
+      <c r="D14">
+        <v>10560</v>
+      </c>
+      <c r="E14">
+        <v>104.3181818181818</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>65-69</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>9510</v>
+      </c>
+      <c r="D15">
+        <v>8949</v>
+      </c>
+      <c r="E15">
+        <v>106.2688568555146</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>70-74</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>6578</v>
+      </c>
+      <c r="D16">
+        <v>6415</v>
+      </c>
+      <c r="E16">
+        <v>102.5409197194076</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>75-79</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>4740</v>
+      </c>
+      <c r="D17">
+        <v>4260</v>
+      </c>
+      <c r="E17">
+        <v>111.2676056338028</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Magallanes y la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>80+</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>6299</v>
+      </c>
+      <c r="D18">
+        <v>5494</v>
+      </c>
+      <c r="E18">
+        <v>114.6523480160175</v>
       </c>
     </row>
   </sheetData>
